--- a/internal_doc/05.测试设计/可靠性测试/aggregate故障测试设计_review.xlsx
+++ b/internal_doc/05.测试设计/可靠性测试/aggregate故障测试设计_review.xlsx
@@ -8,8 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="4" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$36</definedName>
@@ -116,7 +115,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="91">
   <si>
     <t>1、普通拥塞
 2、时间设置超过9s延迟</t>
@@ -163,14 +162,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>dataRG连续降备</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>dataRG备节点故障</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>故障恢复后数据没有丢失，重新操作成功</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -205,15 +196,6 @@
   <si>
     <t>闪断2s、9s，超过7S后重新选主</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>catalog备节点异常重启</t>
-  </si>
-  <si>
-    <t>dataRG主节点异常重启</t>
-  </si>
-  <si>
-    <t>catalog主节点异常重启</t>
   </si>
   <si>
     <t>网络单通（低优先级）</t>
@@ -1000,7 +982,7 @@
         <v>6</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>7</v>
@@ -1020,22 +1002,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D2" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="E2" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E2" s="7" t="s">
-        <v>73</v>
-      </c>
       <c r="F2" s="4" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1044,7 +1026,7 @@
       <c r="C3" s="8"/>
       <c r="D3" s="10"/>
       <c r="E3" s="11" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="F3" s="7"/>
       <c r="G3" s="7"/>
@@ -1054,16 +1036,16 @@
       <c r="B4" s="7"/>
       <c r="C4" s="8"/>
       <c r="D4" s="7" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="94.5">
@@ -1071,16 +1053,16 @@
       <c r="B5" s="7"/>
       <c r="C5" s="8"/>
       <c r="D5" s="14" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>52</v>
+        <v>47</v>
       </c>
       <c r="F5" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="G5" s="7" t="s">
         <v>54</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="40.5">
@@ -1088,22 +1070,22 @@
         <v>2</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="81">
@@ -1111,13 +1093,13 @@
       <c r="B7" s="7"/>
       <c r="C7" s="8"/>
       <c r="D7" s="14" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="G7" s="7"/>
     </row>
@@ -1127,10 +1109,10 @@
       <c r="C8" s="8"/>
       <c r="D8" s="14"/>
       <c r="E8" s="7" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="G8" s="7"/>
     </row>
@@ -1139,19 +1121,19 @@
         <v>3</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>0</v>
@@ -1162,13 +1144,13 @@
       <c r="B10" s="7"/>
       <c r="C10" s="8"/>
       <c r="D10" s="14" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="G10" s="7"/>
     </row>
@@ -1178,29 +1160,29 @@
       <c r="C11" s="8"/>
       <c r="D11" s="14"/>
       <c r="E11" s="7" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
     </row>
     <row r="12" spans="1:7" ht="40.5">
       <c r="A12" s="4" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="G12" s="4"/>
     </row>
@@ -1209,13 +1191,13 @@
       <c r="B13" s="7"/>
       <c r="C13" s="8"/>
       <c r="D13" s="14" t="s">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="G13" s="7"/>
     </row>
@@ -1225,29 +1207,29 @@
       <c r="C14" s="8"/>
       <c r="D14" s="14"/>
       <c r="E14" s="7" t="s">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
     </row>
     <row r="15" spans="1:7" ht="40.5">
       <c r="A15" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G15" s="4"/>
     </row>
@@ -1257,34 +1239,34 @@
       <c r="C16" s="8"/>
       <c r="D16" s="14"/>
       <c r="E16" s="7" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="F16" s="7" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="G16" s="7"/>
     </row>
     <row r="17" spans="1:7" ht="40.5">
       <c r="A17" s="4" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D17" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="F17" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E17" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>39</v>
-      </c>
       <c r="G17" s="4" t="s">
-        <v>29</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -1293,65 +1275,65 @@
       <c r="C18" s="8"/>
       <c r="D18" s="14"/>
       <c r="E18" s="7" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="F18" s="7"/>
       <c r="G18" s="7"/>
     </row>
     <row r="19" spans="1:7" ht="67.5">
       <c r="A19" s="4" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="E19" s="4"/>
       <c r="F19" s="4" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
     </row>
     <row r="20" spans="1:7" ht="27">
       <c r="A20" s="7"/>
       <c r="B20" s="7"/>
       <c r="C20" s="7" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="E20" s="7"/>
       <c r="F20" s="7" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="G20" s="7"/>
     </row>
     <row r="21" spans="1:7" ht="40.5">
       <c r="A21" s="4" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="G21" s="4"/>
     </row>
@@ -1361,29 +1343,29 @@
       <c r="C22" s="8"/>
       <c r="D22" s="14"/>
       <c r="E22" s="7" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="F22" s="7"/>
       <c r="G22" s="7"/>
     </row>
     <row r="23" spans="1:7" ht="40.5">
       <c r="A23" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="G23" s="4"/>
     </row>
@@ -1393,29 +1375,29 @@
       <c r="C24" s="8"/>
       <c r="D24" s="14"/>
       <c r="E24" s="7" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="F24" s="7"/>
       <c r="G24" s="7"/>
     </row>
     <row r="25" spans="1:7" ht="40.5">
       <c r="A25" s="4" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="G25" s="4"/>
     </row>
@@ -1425,29 +1407,29 @@
       <c r="C26" s="8"/>
       <c r="D26" s="14"/>
       <c r="E26" s="7" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="F26" s="7"/>
       <c r="G26" s="7"/>
     </row>
     <row r="27" spans="1:7" ht="40.5">
       <c r="A27" s="4" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="G27" s="4"/>
     </row>
@@ -1457,7 +1439,7 @@
       <c r="C28" s="8"/>
       <c r="D28" s="14"/>
       <c r="E28" s="7" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="F28" s="7"/>
       <c r="G28" s="7"/>
@@ -1467,19 +1449,19 @@
         <v>4</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="G29" s="4"/>
     </row>
@@ -1489,24 +1471,24 @@
       <c r="C30" s="8"/>
       <c r="D30" s="14"/>
       <c r="E30" s="7" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="F30" s="7"/>
       <c r="G30" s="7"/>
     </row>
     <row r="31" spans="1:7" ht="67.5">
       <c r="A31" s="4" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D31" s="4"/>
       <c r="E31" s="4" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="F31" s="4"/>
       <c r="G31" s="13"/>
@@ -1522,23 +1504,23 @@
     </row>
     <row r="33" spans="1:7" ht="54">
       <c r="A33" s="4" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="D33" s="4"/>
       <c r="E33" s="4" t="s">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1552,16 +1534,16 @@
     </row>
     <row r="35" spans="1:7" ht="40.5">
       <c r="A35" s="4" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C35" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E35" s="4"/>
       <c r="F35" s="4"/>
@@ -1573,38 +1555,38 @@
       <c r="C36" s="7"/>
       <c r="D36" s="7"/>
       <c r="E36" s="7" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F36" s="7"/>
       <c r="G36" s="7"/>
     </row>
     <row r="37" spans="1:7" ht="40.5">
       <c r="A37" s="4" t="s">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="G37" s="4"/>
     </row>
     <row r="38" spans="1:7" ht="40.5">
       <c r="A38" s="4" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C38" s="5"/>
       <c r="D38" s="4"/>
@@ -1647,134 +1629,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A22"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
-  <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3" s="7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8" s="7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1">
-      <c r="A9" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1">
-      <c r="A10" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" s="7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1">
-      <c r="A12" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" s="7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1">
-      <c r="A14" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1">
-      <c r="A15" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" s="7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1">
-      <c r="A17" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="18" spans="1:1">
-      <c r="A18" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="19" spans="1:1">
-      <c r="A19" s="7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="20" spans="1:1">
-      <c r="A20" s="7" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:1">
-      <c r="A21" s="7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="22" spans="1:1">
-      <c r="A22" s="7" t="s">
-        <v>24</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/internal_doc/05.测试设计/可靠性测试/aggregate故障测试设计_review.xlsx
+++ b/internal_doc/05.测试设计/可靠性测试/aggregate故障测试设计_review.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Sheet2" sheetId="4" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$G$37</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
@@ -84,7 +84,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A25" authorId="0">
+    <comment ref="A26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -115,7 +115,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="94">
   <si>
     <t>1、普通拥塞
 2、时间设置超过9s延迟</t>
@@ -226,10 +226,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>同断网，另考虑coord、catalog、dataRG组合的场景，如下：</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>聚集</t>
   </si>
   <si>
@@ -259,15 +255,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>断网后组内重新选主；恢复网络后在新主查询的数据正确；断网之前没有数据更新则网络恢复后aggregate查询的数据在断网前后一致；</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>故障恢复后数据没有丢失，重新操作成功</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>insert数据的同时aggregate</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -373,10 +361,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>$project/$match/$limit/$skip/$group/$sort</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1、查询操作成功，结果返回正确；  2、查询失败，返回正确的错误提示信息；故障恢复后重新操作成功；</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -478,6 +462,34 @@
   </si>
   <si>
     <t>故障恢复后数据没有丢失，重新操作成功</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>aggregate组合查询</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dataRG主节点所在目录umount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>coord节点所在目录umount</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dataRG备节点所在服务器内存耗尽</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>insert数据的同时aggregate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>coor节点与其他节点网络单通</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dataRG主节点与其他备节点网络单通</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -961,7 +973,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G43"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="9.25" style="6" customWidth="1"/>
@@ -1002,22 +1014,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>31</v>
+        <v>87</v>
       </c>
       <c r="D2" s="13" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -1026,7 +1038,7 @@
       <c r="C3" s="8"/>
       <c r="D3" s="10"/>
       <c r="E3" s="11" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="F3" s="7"/>
       <c r="G3" s="7"/>
@@ -1036,16 +1048,16 @@
       <c r="B4" s="7"/>
       <c r="C4" s="8"/>
       <c r="D4" s="7" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>23</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="94.5">
@@ -1053,16 +1065,16 @@
       <c r="B5" s="7"/>
       <c r="C5" s="8"/>
       <c r="D5" s="14" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="40.5">
@@ -1070,19 +1082,19 @@
         <v>2</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C6" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>29</v>
-      </c>
       <c r="E6" s="4" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G6" s="4" t="s">
         <v>19</v>
@@ -1093,13 +1105,13 @@
       <c r="B7" s="7"/>
       <c r="C7" s="8"/>
       <c r="D7" s="14" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G7" s="7"/>
     </row>
@@ -1109,10 +1121,10 @@
       <c r="C8" s="8"/>
       <c r="D8" s="14"/>
       <c r="E8" s="7" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>90</v>
+        <v>11</v>
       </c>
       <c r="G8" s="7"/>
     </row>
@@ -1121,19 +1133,19 @@
         <v>3</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>29</v>
-      </c>
       <c r="E9" s="4" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G9" s="4" t="s">
         <v>0</v>
@@ -1144,13 +1156,13 @@
       <c r="B10" s="7"/>
       <c r="C10" s="8"/>
       <c r="D10" s="14" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G10" s="7"/>
     </row>
@@ -1160,29 +1172,29 @@
       <c r="C11" s="8"/>
       <c r="D11" s="14"/>
       <c r="E11" s="7" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
     </row>
     <row r="12" spans="1:7" ht="40.5">
       <c r="A12" s="4" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B12" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>29</v>
-      </c>
       <c r="E12" s="4" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G12" s="4"/>
     </row>
@@ -1191,13 +1203,13 @@
       <c r="B13" s="7"/>
       <c r="C13" s="8"/>
       <c r="D13" s="14" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="G13" s="7"/>
     </row>
@@ -1207,7 +1219,7 @@
       <c r="C14" s="8"/>
       <c r="D14" s="14"/>
       <c r="E14" s="7" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
@@ -1217,409 +1229,437 @@
         <v>12</v>
       </c>
       <c r="B15" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C15" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>29</v>
-      </c>
       <c r="E15" s="4" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F15" s="4" t="s">
         <v>11</v>
       </c>
       <c r="G15" s="4"/>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" ht="81">
       <c r="A16" s="7"/>
       <c r="B16" s="7"/>
       <c r="C16" s="8"/>
-      <c r="D16" s="14"/>
+      <c r="D16" s="14" t="s">
+        <v>45</v>
+      </c>
       <c r="E16" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="G16" s="7"/>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="G17" s="7"/>
+    </row>
+    <row r="18" spans="1:7" ht="40.5">
+      <c r="A18" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C18" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+    </row>
+    <row r="20" spans="1:7" ht="67.5">
+      <c r="A20" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E20" s="4"/>
+      <c r="F20" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="27">
+      <c r="A21" s="7"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="G21" s="7"/>
+    </row>
+    <row r="22" spans="1:7" ht="40.5">
+      <c r="A22" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G22" s="4"/>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="7"/>
+      <c r="B23" s="7"/>
+      <c r="C23" s="8"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="F16" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="G16" s="7"/>
-    </row>
-    <row r="17" spans="1:7" ht="40.5">
-      <c r="A17" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17" s="4" t="s">
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
+    </row>
+    <row r="24" spans="1:7" ht="40.5">
+      <c r="A24" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D24" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C17" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D17" s="4" t="s">
+      <c r="E24" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G24" s="4"/>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" s="7"/>
+      <c r="B25" s="7"/>
+      <c r="C25" s="8"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+    </row>
+    <row r="26" spans="1:7" ht="40.5">
+      <c r="A26" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C26" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E17" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="8"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-    </row>
-    <row r="19" spans="1:7" ht="67.5">
-      <c r="A19" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="B19" s="4" t="s">
+      <c r="D26" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C19" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="27">
-      <c r="A20" s="7"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D20" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="G20" s="7"/>
-    </row>
-    <row r="21" spans="1:7" ht="40.5">
-      <c r="A21" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B21" s="4" t="s">
+      <c r="E26" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G26" s="4"/>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" s="7"/>
+      <c r="B27" s="7"/>
+      <c r="C27" s="8"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="F27" s="7"/>
+      <c r="G27" s="7"/>
+    </row>
+    <row r="28" spans="1:7" ht="40.5">
+      <c r="A28" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C28" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D28" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="E28" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G28" s="4"/>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="7"/>
+      <c r="B29" s="7"/>
+      <c r="C29" s="8"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
+    </row>
+    <row r="30" spans="1:7" ht="40.5">
+      <c r="A30" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F30" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="G30" s="4"/>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="7"/>
+      <c r="B31" s="7"/>
+      <c r="C31" s="8"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="F31" s="7"/>
+      <c r="G31" s="7"/>
+    </row>
+    <row r="32" spans="1:7" ht="67.5">
+      <c r="A32" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C32" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="D32" s="4"/>
+      <c r="E32" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="F32" s="4"/>
+      <c r="G32" s="13"/>
+    </row>
+    <row r="33" spans="1:7">
+      <c r="A33" s="7"/>
+      <c r="B33" s="7"/>
+      <c r="C33" s="8"/>
+      <c r="D33" s="7"/>
+      <c r="E33" s="7"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="7"/>
+    </row>
+    <row r="34" spans="1:7" ht="54">
+      <c r="A34" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C34" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D34" s="4"/>
+      <c r="E34" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F34" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="G34" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
+      <c r="A35" s="7"/>
+      <c r="B35" s="7"/>
+      <c r="C35" s="8"/>
+      <c r="D35" s="7"/>
+      <c r="E35" s="7"/>
+      <c r="F35" s="7"/>
+      <c r="G35" s="7"/>
+    </row>
+    <row r="36" spans="1:7" ht="40.5">
+      <c r="A36" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C36" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E21" s="4" t="s">
-        <v>80</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="G21" s="4"/>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="7"/>
-      <c r="B22" s="7"/>
-      <c r="C22" s="8"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="7" t="s">
-        <v>81</v>
-      </c>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
-    </row>
-    <row r="23" spans="1:7" ht="40.5">
-      <c r="A23" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="B23" s="4" t="s">
+      <c r="D36" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C23" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="G23" s="4"/>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="7"/>
-      <c r="B24" s="7"/>
-      <c r="C24" s="8"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="F24" s="7"/>
-      <c r="G24" s="7"/>
-    </row>
-    <row r="25" spans="1:7" ht="40.5">
-      <c r="A25" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C25" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="G25" s="4"/>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="7"/>
-      <c r="B26" s="7"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="F26" s="7"/>
-      <c r="G26" s="7"/>
-    </row>
-    <row r="27" spans="1:7" ht="40.5">
-      <c r="A27" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C27" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="G27" s="4"/>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28" s="7"/>
-      <c r="B28" s="7"/>
-      <c r="C28" s="8"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="F28" s="7"/>
-      <c r="G28" s="7"/>
-    </row>
-    <row r="29" spans="1:7" ht="40.5">
-      <c r="A29" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="G29" s="4"/>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30" s="7"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="8"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="F30" s="7"/>
-      <c r="G30" s="7"/>
-    </row>
-    <row r="31" spans="1:7" ht="67.5">
-      <c r="A31" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C31" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="F31" s="4"/>
-      <c r="G31" s="13"/>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32" s="7"/>
-      <c r="B32" s="7"/>
-      <c r="C32" s="8"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
-      <c r="G32" s="7"/>
-    </row>
-    <row r="33" spans="1:7" ht="54">
-      <c r="A33" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C33" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="F33" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G33" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34" s="7"/>
-      <c r="B34" s="7"/>
-      <c r="C34" s="8"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="7"/>
-      <c r="G34" s="7"/>
-    </row>
-    <row r="35" spans="1:7" ht="40.5">
-      <c r="A35" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C35" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D35" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-    </row>
-    <row r="36" spans="1:7" ht="40.5">
-      <c r="A36" s="7"/>
-      <c r="B36" s="7"/>
-      <c r="C36" s="7"/>
-      <c r="D36" s="7"/>
-      <c r="E36" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="F36" s="7"/>
-      <c r="G36" s="7"/>
-    </row>
-    <row r="37" spans="1:7" ht="40.5">
-      <c r="A37" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C37" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E37" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="G37" s="4"/>
+      <c r="E36" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+    </row>
+    <row r="37" spans="1:7" ht="27">
+      <c r="A37" s="7"/>
+      <c r="B37" s="7"/>
+      <c r="C37" s="7"/>
+      <c r="D37" s="7"/>
+      <c r="E37" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="F37" s="7"/>
+      <c r="G37" s="7"/>
     </row>
     <row r="38" spans="1:7" ht="40.5">
       <c r="A38" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B38" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C38" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D38" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C38" s="5"/>
-      <c r="D38" s="4"/>
-      <c r="E38" s="4"/>
-      <c r="F38" s="4"/>
+      <c r="E38" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>58</v>
+      </c>
       <c r="G38" s="4"/>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" ht="27">
       <c r="A39" s="7"/>
       <c r="B39" s="7"/>
       <c r="C39" s="8"/>
-      <c r="D39" s="7"/>
-      <c r="E39" s="7"/>
+      <c r="D39" s="14"/>
+      <c r="E39" s="7" t="s">
+        <v>89</v>
+      </c>
       <c r="F39" s="7"/>
       <c r="G39" s="7"/>
     </row>
-    <row r="40" spans="1:7">
-      <c r="A40" s="7"/>
-      <c r="B40" s="7"/>
-      <c r="C40" s="8"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="7"/>
-      <c r="G40" s="7"/>
+    <row r="40" spans="1:7" ht="40.5">
+      <c r="A40" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C40" s="5"/>
+      <c r="D40" s="4"/>
+      <c r="E40" s="4"/>
+      <c r="F40" s="4"/>
+      <c r="G40" s="4"/>
     </row>
     <row r="41" spans="1:7">
-      <c r="D41" s="9"/>
-      <c r="E41" s="9"/>
-      <c r="F41" s="9"/>
-      <c r="G41" s="9"/>
+      <c r="A41" s="7"/>
+      <c r="B41" s="7"/>
+      <c r="C41" s="8"/>
+      <c r="D41" s="7"/>
+      <c r="E41" s="7"/>
+      <c r="F41" s="7"/>
+      <c r="G41" s="7"/>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42" s="7"/>
+      <c r="B42" s="7"/>
+      <c r="C42" s="8"/>
+      <c r="D42" s="7"/>
+      <c r="E42" s="7"/>
+      <c r="F42" s="7"/>
+      <c r="G42" s="7"/>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="D43" s="9"/>
+      <c r="E43" s="9"/>
+      <c r="F43" s="9"/>
+      <c r="G43" s="9"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G36"/>
+  <autoFilter ref="A1:G37"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
